--- a/data_voor_swing/aggregatietabellen/uitrustingsgraad_gewest.xlsx
+++ b/data_voor_swing/aggregatietabellen/uitrustingsgraad_gewest.xlsx
@@ -1,41 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <workbookPr showObjects="all" updateLinks="userSet" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" xWindow="480" yWindow="75" windowWidth="18075" windowHeight="12525" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="uitrustingsgraad_gewest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="auto" refMode="A1" iterateCount="100"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+  <si>
+    <t>uitrustingsgraad</t>
+  </si>
+  <si>
+    <t>gewest</t>
+  </si>
+  <si>
+    <t>a0</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>b0</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>c0</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.000000000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
-    <numFmt numFmtId="175" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="0.000000000000"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="179" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="180" formatCode="0.0000000000000000"/>
-  </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -51,7 +81,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,35 +89,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,106 +410,84 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="0" outlineLevel="0">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>uitrustingsgraad</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>gewest</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="0" outlineLevel="0">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>a0</t>
-        </is>
-      </c>
-      <c r="B2" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="0" outlineLevel="0">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="B3" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="0" outlineLevel="0">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="B4" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="0" outlineLevel="0">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>b0</t>
-        </is>
-      </c>
-      <c r="B5" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="0" outlineLevel="0">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="0" outlineLevel="0">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>c0</t>
-        </is>
-      </c>
-      <c r="B7" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="0" outlineLevel="0">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>c1</t>
-        </is>
-      </c>
-      <c r="B8" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="0" outlineLevel="0">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="0" outlineLevel="0">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>c3</t>
-        </is>
-      </c>
-      <c r="B10" s="23">
-        <v>2000</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
